--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -3698,7 +3698,7 @@
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Close the remaining Maintenance Scheduler API subtasks.</t>
+          <t>Close the remaining Maintenance Scheduler API subtasks. DEV-01/02/03 verified working; TEST-01 and FIX-01 closed by fixing two defects found while testing: the KM range was not ordered (a job from Km 40 to Km 10 saved cleanly, giving every consumer a negative span), and DELETE ignored rowCount so a missing id answered 200 "Deleted" and wrote an audit entry for a deletion that never happened. STILL OPEN: UAT-01 needs real maintenance coordinators - not something that can be closed from the code.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="H14" s="42" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I14" s="70" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Test the scheduler end to end from the UI.</t>
+          <t>Test the scheduler end to end from the UI. 26 checks pass: 16 against the endpoints and 10 driven through the real interface signed in as a Data Analyst - form opens and accepts an entry, it appears in the list, detail panel opens, edit persists, delete asks for confirmation, the row leaves the list and is still gone after a reload. Screenshots in manuscript-figures/ for the QA section.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I15" s="70" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="H16" s="42" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I16" s="70" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2389,7 +2389,7 @@
         <v>2.517</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>1.888</v>
+        <v>2.203</v>
       </c>
       <c r="G23" s="38" t="inlineStr">
         <is>
@@ -3149,6 +3149,10 @@
         <v/>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <autoFilter ref="A4:L34"/>
   <mergeCells count="1">
@@ -3698,7 +3702,7 @@
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Close the remaining Maintenance Scheduler API subtasks. DEV-01/02/03 verified working; TEST-01 and FIX-01 closed by fixing two defects found while testing: the KM range was not ordered (a job from Km 40 to Km 10 saved cleanly, giving every consumer a negative span), and DELETE ignored rowCount so a missing id answered 200 "Deleted" and wrote an audit entry for a deletion that never happened. STILL OPEN: UAT-01 needs real maintenance coordinators - not something that can be closed from the code.</t>
+          <t>Close the remaining Maintenance Scheduler API subtasks. DONE: DEV-01/02/03 verified; TEST-01 and FIX-01 closed by fixing two defects found while testing - the KM range was not ordered (Km 40 to Km 10 saved cleanly, giving every consumer a negative span), and DELETE ignored rowCount so a missing id answered 200 "Deleted" and wrote an audit entry for a deletion that never happened. MAINT is now 7 of 8 subtasks (2.203 of 2.517). STILL OPEN - UAT-01: the interface must be evaluated by maintenance coordinators who can confirm they can plan and organise roadwork with it. That needs real evaluators, not code. ALSO: the existing "Toll Booth Repair" row is entered as Km 76.25 to 73.23 (reversed) and is in progress - correct it by hand; the new validation stops another but does not repair that one.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3708,7 +3712,7 @@
       </c>
       <c r="H14" s="42" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="I14" s="70" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3149,10 +3149,6 @@
         <v/>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
   </sheetData>
   <autoFilter ref="A4:L34"/>
   <mergeCells count="1">
@@ -3702,7 +3698,7 @@
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Close the remaining Maintenance Scheduler API subtasks. DONE: DEV-01/02/03 verified; TEST-01 and FIX-01 closed by fixing two defects found while testing - the KM range was not ordered (Km 40 to Km 10 saved cleanly, giving every consumer a negative span), and DELETE ignored rowCount so a missing id answered 200 "Deleted" and wrote an audit entry for a deletion that never happened. MAINT is now 7 of 8 subtasks (2.203 of 2.517). STILL OPEN - UAT-01: the interface must be evaluated by maintenance coordinators who can confirm they can plan and organise roadwork with it. That needs real evaluators, not code. ALSO: the existing "Toll Booth Repair" row is entered as Km 76.25 to 73.23 (reversed) and is in progress - correct it by hand; the new validation stops another but does not repair that one.</t>
+          <t>Close the remaining Maintenance Scheduler API subtasks. DONE: DEV-01/02/03 verified; TEST-01 and FIX-01 closed by fixing two defects found while testing - the KM range was not ordered (Km 40 to Km 10 saved cleanly, giving every consumer a negative span), and DELETE ignored rowCount so a missing id answered 200 "Deleted" and wrote an audit entry for a deletion that never happened. MAINT is now 7 of 8 subtasks (2.203 of 2.517). STILL OPEN - UAT-01: the interface must be evaluated by maintenance coordinators who can confirm they can plan and organise roadwork with it. That needs real evaluators, not code. ALSO: the existing "Toll Booth Repair" row is entered as Km 76.25 to 73.23 (reversed) and is in progress - correct it by hand; the new validation stops another but does not repair that one. QA PASS (2 Oct): 24 adversarial checks - boundaries, malformed timestamps, script/SQL payloads, bad ids, invalid status transitions. One more defect found and fixed: a malformed id reached Postgres, which threw, and the service reports every query failure as 'database not reachable', so a typo answered 503 and would have raised an infrastructure alarm. Now 404. OPEN DESIGN GAP: status is never reconciled with the clock. Both rows have windows that closed in August; one still reads in_progress so the page claims 3.0 km 'under work right now' for work that ended 46 days ago, and the other reads scheduled so the tile shows 1 beside 'nothing upcoming'. Fix before any demo.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -197,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -376,6 +376,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1143,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1251,29 +1252,29 @@
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>INCIDENTFC</t>
+          <t>AUTH</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>Incident Predictive Model</t>
+          <t>Authentication &amp; Session Management (frontend)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>MOD-ANA</t>
+          <t>MOD-FE</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>Jertz</t>
+          <t>Kiarra</t>
         </is>
       </c>
       <c r="E5" s="23" t="n">
-        <v>2.832</v>
+        <v>1.888</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>0</v>
+        <v>1.259</v>
       </c>
       <c r="G5" s="57" t="inlineStr">
         <is>
@@ -1294,7 +1295,7 @@
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
-          <t>Sep 29 - Oct 3</t>
+          <t>Oct 5 - Oct 6</t>
         </is>
       </c>
       <c r="L5" s="22">
@@ -1311,55 +1312,55 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>MODEVAL</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>Model Evaluation &amp; Validation</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>MOD-ANA</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>TRAFFIC</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Traffic Overview Dashboard (frontend)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>Hans</t>
         </is>
       </c>
-      <c r="E6" s="28" t="n">
-        <v>4.406</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="G6" s="38" t="inlineStr">
+      <c r="E6" s="23" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="G6" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="23">
         <f>IF(UPPER(G6)="Y",E6,IF(N6=0,F6,F6+(E6-F6)*M6/N6))</f>
         <v/>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="25">
         <f>E6-H6</f>
         <v/>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="26">
         <f>IFERROR(H6/E6,0)</f>
         <v/>
       </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>Sep 29 - Oct 3</t>
-        </is>
-      </c>
-      <c r="L6" s="9">
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L6" s="22">
         <f>IF(H6&gt;=E6,"Done",IF(H6&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1375,29 +1376,29 @@
     <row r="7">
       <c r="A7" s="21" t="inlineStr">
         <is>
-          <t>PRESCRIBE</t>
+          <t>INCIDENT</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>Prescriptive Optimization Models</t>
+          <t>Incident Data API Endpoints (frontend)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>MOD-ANA</t>
+          <t>MOD-FE</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>Hans</t>
+          <t>Jertz</t>
         </is>
       </c>
       <c r="E7" s="23" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="F7" s="24" t="n">
         <v>2.517</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <v>0</v>
       </c>
       <c r="G7" s="57" t="inlineStr">
         <is>
@@ -1418,7 +1419,7 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>Sep 29 - Oct 3</t>
+          <t>Oct 5 - Oct 6</t>
         </is>
       </c>
       <c r="L7" s="22">
@@ -1435,117 +1436,117 @@
       </c>
     </row>
     <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>DESCOPED - delivered as an LLM layer instead. GLM via an OpenAI-compatible endpoint, with the ai-insight, ai-explain and sandbox-command services; ai-explain retrieves from the warehouse and grounds the prompt. Not built: document corpus, chunking, embeddings, vector index, Claude Sonnet, FastAPI. Confirm with the adviser that the substitution is accepted - 2.517 points ride on it.</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>MOD-ANA</t>
-        </is>
-      </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>SANDBOX</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>AI Traffic Sandbox API (frontend)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>Ysa</t>
         </is>
       </c>
-      <c r="E8" s="72" t="n">
+      <c r="E8" s="23" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="G8" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H8" s="23">
+        <f>IF(UPPER(G8)="Y",E8,IF(N8=0,F8,F8+(E8-F8)*M8/N8))</f>
+        <v/>
+      </c>
+      <c r="I8" s="25">
+        <f>E8-H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="26">
+        <f>IFERROR(H8/E8,0)</f>
+        <v/>
+      </c>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L8" s="22">
+        <f>IF(H8&gt;=E8,"Done",IF(H8&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M8" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A8&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A8&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A8&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A8&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N8" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A8&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A8&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A8&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A8&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>MAINT</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Maintenance Scheduler API (frontend)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
         <v>2.517</v>
       </c>
-      <c r="F8" s="73" t="n">
-        <v>1.438</v>
-      </c>
-      <c r="G8" s="56" t="inlineStr">
+      <c r="F9" s="24" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="G9" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H8" s="72">
-        <f>IF(UPPER(G8)="Y",E8,IF(N8=0,F8,F8+(E8-F8)*M8/N8))</f>
-        <v/>
-      </c>
-      <c r="I8" s="74">
-        <f>E8-H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="75">
-        <f>IFERROR(H8/E8,0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="39" t="inlineStr">
-        <is>
-          <t>Oct 3 - sign-off</t>
-        </is>
-      </c>
-      <c r="L8" s="39">
-        <f>IF(H8&gt;=E8,"Done",IF(H8&gt;0,"In progress","Not started"))</f>
-        <v/>
-      </c>
-      <c r="M8" s="76">
-        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A8&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A8&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A8&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A8&amp;";*",Ysa!$H:$H,"Done")</f>
-        <v/>
-      </c>
-      <c r="N8" s="76">
-        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A8&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A8&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A8&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A8&amp;";*")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>MAPCOMP</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Map Comparison API</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>MOD-BE</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Jertz</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>2.832</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>1.573</v>
-      </c>
-      <c r="G9" s="38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H9" s="28">
+      <c r="H9" s="23">
         <f>IF(UPPER(G9)="Y",E9,IF(N9=0,F9,F9+(E9-F9)*M9/N9))</f>
         <v/>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="25">
         <f>E9-H9</f>
         <v/>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="26">
         <f>IFERROR(H9/E9,0)</f>
         <v/>
       </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>Oct 3 - Oct 5</t>
-        </is>
-      </c>
-      <c r="L9" s="9">
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L9" s="22">
         <f>IF(H9&gt;=E9,"Done",IF(H9&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1559,55 +1560,55 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>DATAPREP</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Analytics Data Preparation &amp; Integration</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>MOD-ANA</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Hans</t>
-        </is>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>4.406</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>3.147</v>
-      </c>
-      <c r="G10" s="38" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>MAPCOMP</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Map Comparison API (frontend)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G10" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="23">
         <f>IF(UPPER(G10)="Y",E10,IF(N10=0,F10,F10+(E10-F10)*M10/N10))</f>
         <v/>
       </c>
-      <c r="I10" s="30">
+      <c r="I10" s="25">
         <f>E10-H10</f>
         <v/>
       </c>
-      <c r="J10" s="31">
+      <c r="J10" s="26">
         <f>IFERROR(H10/E10,0)</f>
         <v/>
       </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>Oct 4 - Oct 5</t>
-        </is>
-      </c>
-      <c r="L10" s="9">
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>Oct 3 - Oct 5</t>
+        </is>
+      </c>
+      <c r="L10" s="22">
         <f>IF(H10&gt;=E10,"Done",IF(H10&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1621,55 +1622,55 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Core Traffic Data Schema &amp; Import Tables</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>MOD-DB</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>SUSTAIN</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Sustainability &amp; Emissions API (frontend)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Hans</t>
         </is>
       </c>
-      <c r="E11" s="28" t="n">
-        <v>3.147</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="G11" s="38" t="inlineStr">
+      <c r="E11" s="23" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="G11" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="23">
         <f>IF(UPPER(G11)="Y",E11,IF(N11=0,F11,F11+(E11-F11)*M11/N11))</f>
         <v/>
       </c>
-      <c r="I11" s="30">
+      <c r="I11" s="25">
         <f>E11-H11</f>
         <v/>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="26">
         <f>IFERROR(H11/E11,0)</f>
         <v/>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>Oct 4 - Oct 5</t>
         </is>
       </c>
-      <c r="L11" s="9">
+      <c r="L11" s="22">
         <f>IF(H11&gt;=E11,"Done",IF(H11&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1683,55 +1684,55 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>SUSTAIN</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Sustainability &amp; Emissions API</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>MOD-BE</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Hans</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="n">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>DATAUP</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Data Management &amp; Upload Page</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
         <v>2.517</v>
       </c>
-      <c r="F12" s="29" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="G12" s="38" t="inlineStr">
+      <c r="F12" s="24" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="G12" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="23">
         <f>IF(UPPER(G12)="Y",E12,IF(N12=0,F12,F12+(E12-F12)*M12/N12))</f>
         <v/>
       </c>
-      <c r="I12" s="30">
+      <c r="I12" s="25">
         <f>E12-H12</f>
         <v/>
       </c>
-      <c r="J12" s="31">
+      <c r="J12" s="26">
         <f>IFERROR(H12/E12,0)</f>
         <v/>
       </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>Oct 4 - Oct 5</t>
-        </is>
-      </c>
-      <c r="L12" s="9">
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L12" s="22">
         <f>IF(H12&gt;=E12,"Done",IF(H12&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1745,55 +1746,55 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>SANDBOX</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>AI Traffic Sandbox API</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>MOD-BE</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>Ysa</t>
-        </is>
-      </c>
-      <c r="E13" s="28" t="n">
-        <v>2.832</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="G13" s="38" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>AUDIT</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Audit Log API (frontend)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>MOD-FE</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G13" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="23">
         <f>IF(UPPER(G13)="Y",E13,IF(N13=0,F13,F13+(E13-F13)*M13/N13))</f>
         <v/>
       </c>
-      <c r="I13" s="30">
+      <c r="I13" s="25">
         <f>E13-H13</f>
         <v/>
       </c>
-      <c r="J13" s="31">
+      <c r="J13" s="26">
         <f>IFERROR(H13/E13,0)</f>
         <v/>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="22">
         <f>IF(H13&gt;=E13,"Done",IF(H13&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1807,55 +1808,55 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>HOST</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hosting &amp; Deployment Setup</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>AUTH</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Authentication &amp; Session Management (backend/API)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>Kiarra</t>
         </is>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="23" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="F14" s="24" t="n">
         <v>1.573</v>
       </c>
-      <c r="F14" s="29" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="G14" s="38" t="inlineStr">
+      <c r="G14" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="23">
         <f>IF(UPPER(G14)="Y",E14,IF(N14=0,F14,F14+(E14-F14)*M14/N14))</f>
         <v/>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="25">
         <f>E14-H14</f>
         <v/>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="26">
         <f>IFERROR(H14/E14,0)</f>
         <v/>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="22">
         <f>IF(H14&gt;=E14,"Done",IF(H14&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1869,55 +1870,55 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>CACHE</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Redis Cache &amp; Event Messaging Setup</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>MOD-DB</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>TRAFFIC</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Traffic Overview Dashboard (backend/API)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>Hans</t>
         </is>
       </c>
-      <c r="E15" s="28" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="G15" s="38" t="inlineStr">
+      <c r="E15" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="G15" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="23">
         <f>IF(UPPER(G15)="Y",E15,IF(N15=0,F15,F15+(E15-F15)*M15/N15))</f>
         <v/>
       </c>
-      <c r="I15" s="30">
+      <c r="I15" s="25">
         <f>E15-H15</f>
         <v/>
       </c>
-      <c r="J15" s="31">
+      <c r="J15" s="26">
         <f>IFERROR(H15/E15,0)</f>
         <v/>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L15" s="9">
+      <c r="L15" s="22">
         <f>IF(H15&gt;=E15,"Done",IF(H15&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1931,55 +1932,55 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>TRAFFICFC</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Traffic Volume Predictive Model</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>MOD-ANA</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Hans</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>3.462</v>
-      </c>
-      <c r="F16" s="29" t="n">
-        <v>2.832</v>
-      </c>
-      <c r="G16" s="38" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>INCIDENT</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Incident Data API Endpoints (backend/API)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="G16" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="23">
         <f>IF(UPPER(G16)="Y",E16,IF(N16=0,F16,F16+(E16-F16)*M16/N16))</f>
         <v/>
       </c>
-      <c r="I16" s="30">
+      <c r="I16" s="25">
         <f>E16-H16</f>
         <v/>
       </c>
-      <c r="J16" s="31">
+      <c r="J16" s="26">
         <f>IFERROR(H16/E16,0)</f>
         <v/>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="22">
         <f>IF(H16&gt;=E16,"Done",IF(H16&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -1993,55 +1994,55 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
-        <is>
-          <t>AGENT-S</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Agent Simulation - scenarios &amp; validation</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>MOD-ANA</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>Jertz</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="n">
-        <v>1.102</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="G17" s="38" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>SANDBOX</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>AI Traffic Sandbox API (backend/API)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>Ysa</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G17" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="23">
         <f>IF(UPPER(G17)="Y",E17,IF(N17=0,F17,F17+(E17-F17)*M17/N17))</f>
         <v/>
       </c>
-      <c r="I17" s="30">
+      <c r="I17" s="25">
         <f>E17-H17</f>
         <v/>
       </c>
-      <c r="J17" s="31">
+      <c r="J17" s="26">
         <f>IFERROR(H17/E17,0)</f>
         <v/>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="22">
         <f>IF(H17&gt;=E17,"Done",IF(H17&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2055,55 +2056,55 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>AUDIT</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Audit Log API</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>MAINT</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Maintenance Scheduler API (backend/API)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>MOD-BE</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Jertz</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="n">
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="n">
         <v>2.203</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="24" t="n">
         <v>1.573</v>
       </c>
-      <c r="G18" s="38" t="inlineStr">
+      <c r="G18" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="23">
         <f>IF(UPPER(G18)="Y",E18,IF(N18=0,F18,F18+(E18-F18)*M18/N18))</f>
         <v/>
       </c>
-      <c r="I18" s="30">
+      <c r="I18" s="25">
         <f>E18-H18</f>
         <v/>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="26">
         <f>IFERROR(H18/E18,0)</f>
         <v/>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="22">
         <f>IF(H18&gt;=E18,"Done",IF(H18&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2117,55 +2118,55 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
-        <is>
-          <t>ENV</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Environment Configuration</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Kiarra</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="G19" s="38" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>MAPCOMP</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>Map Comparison API (backend/API)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G19" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="23">
         <f>IF(UPPER(G19)="Y",E19,IF(N19=0,F19,F19+(E19-F19)*M19/N19))</f>
         <v/>
       </c>
-      <c r="I19" s="30">
+      <c r="I19" s="25">
         <f>E19-H19</f>
         <v/>
       </c>
-      <c r="J19" s="31">
+      <c r="J19" s="26">
         <f>IFERROR(H19/E19,0)</f>
         <v/>
       </c>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>Oct 5 - Oct 6</t>
-        </is>
-      </c>
-      <c r="L19" s="9">
+      <c r="K19" s="22" t="inlineStr">
+        <is>
+          <t>Oct 3 - Oct 5</t>
+        </is>
+      </c>
+      <c r="L19" s="22">
         <f>IF(H19&gt;=E19,"Done",IF(H19&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2179,55 +2180,55 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>REALTIME</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Redis Realtime &amp; Event Streaming</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>SUSTAIN</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Sustainability &amp; Emissions API (backend/API)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>MOD-BE</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Ysa</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>2.203</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>1.573</v>
-      </c>
-      <c r="G20" s="38" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="G20" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="23">
         <f>IF(UPPER(G20)="Y",E20,IF(N20=0,F20,F20+(E20-F20)*M20/N20))</f>
         <v/>
       </c>
-      <c r="I20" s="30">
+      <c r="I20" s="25">
         <f>E20-H20</f>
         <v/>
       </c>
-      <c r="J20" s="31">
+      <c r="J20" s="26">
         <f>IFERROR(H20/E20,0)</f>
         <v/>
       </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>Oct 5 - Oct 6</t>
-        </is>
-      </c>
-      <c r="L20" s="9">
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>Oct 4 - Oct 5</t>
+        </is>
+      </c>
+      <c r="L20" s="22">
         <f>IF(H20&gt;=E20,"Done",IF(H20&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2241,55 +2242,55 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
-        <is>
-          <t>AGENT-M</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Agent Simulation - vehicle dynamics &amp; calibration</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>MOD-ANA</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>Hans</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="n">
-        <v>1.101</v>
-      </c>
-      <c r="F21" s="29" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="G21" s="38" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>UPLOAD</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>Data Upload &amp; Validation API</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>Ysa</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F21" s="24" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="G21" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="23">
         <f>IF(UPPER(G21)="Y",E21,IF(N21=0,F21,F21+(E21-F21)*M21/N21))</f>
         <v/>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="25">
         <f>E21-H21</f>
         <v/>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="26">
         <f>IFERROR(H21/E21,0)</f>
         <v/>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="K21" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L21" s="9">
+      <c r="L21" s="22">
         <f>IF(H21&gt;=E21,"Done",IF(H21&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2303,55 +2304,55 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
-        <is>
-          <t>AUTH</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Authentication &amp; Session Management</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>MOD-FE</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Kiarra</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="F22" s="29" t="n">
-        <v>1.259</v>
-      </c>
-      <c r="G22" s="38" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>REALTIME</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Redis Realtime &amp; Event Streaming</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>MOD-BE</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Ysa</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F22" s="24" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G22" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="23">
         <f>IF(UPPER(G22)="Y",E22,IF(N22=0,F22,F22+(E22-F22)*M22/N22))</f>
         <v/>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="25">
         <f>E22-H22</f>
         <v/>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="26">
         <f>IFERROR(H22/E22,0)</f>
         <v/>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K22" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L22" s="9">
+      <c r="L22" s="22">
         <f>IF(H22&gt;=E22,"Done",IF(H22&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2365,55 +2366,55 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>MAINT</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Maintenance Scheduler API</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>AUDIT</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Audit Log API (backend/API)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>MOD-BE</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>Kiarra</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="n">
-        <v>2.517</v>
-      </c>
-      <c r="F23" s="29" t="n">
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="n">
         <v>2.203</v>
       </c>
-      <c r="G23" s="38" t="inlineStr">
+      <c r="F23" s="24" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G23" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="23">
         <f>IF(UPPER(G23)="Y",E23,IF(N23=0,F23,F23+(E23-F23)*M23/N23))</f>
         <v/>
       </c>
-      <c r="I23" s="30">
+      <c r="I23" s="25">
         <f>E23-H23</f>
         <v/>
       </c>
-      <c r="J23" s="31">
+      <c r="J23" s="26">
         <f>IFERROR(H23/E23,0)</f>
         <v/>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="K23" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="22">
         <f>IF(H23&gt;=E23,"Done",IF(H23&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2427,55 +2428,55 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>TRAFFIC</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Traffic Overview Dashboard</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>MOD-FE</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>MODEVAL</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Model Evaluation &amp; Validation</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>Hans</t>
         </is>
       </c>
-      <c r="E24" s="28" t="n">
-        <v>3.147</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>2.832</v>
-      </c>
-      <c r="G24" s="38" t="inlineStr">
+      <c r="E24" s="23" t="n">
+        <v>4.406</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="G24" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="23">
         <f>IF(UPPER(G24)="Y",E24,IF(N24=0,F24,F24+(E24-F24)*M24/N24))</f>
         <v/>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="25">
         <f>E24-H24</f>
         <v/>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="26">
         <f>IFERROR(H24/E24,0)</f>
         <v/>
       </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>Oct 5 - Oct 6</t>
-        </is>
-      </c>
-      <c r="L24" s="9">
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>Sep 29 - Oct 3</t>
+        </is>
+      </c>
+      <c r="L24" s="22">
         <f>IF(H24&gt;=E24,"Done",IF(H24&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2489,55 +2490,55 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>TRAFFICDESC</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>Traffic Volume Descriptive Analytics</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>MOD-ANA</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>Hans</t>
         </is>
       </c>
-      <c r="E25" s="28" t="n">
+      <c r="E25" s="23" t="n">
         <v>2.832</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="24" t="n">
         <v>2.517</v>
       </c>
-      <c r="G25" s="38" t="inlineStr">
+      <c r="G25" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="23">
         <f>IF(UPPER(G25)="Y",E25,IF(N25=0,F25,F25+(E25-F25)*M25/N25))</f>
         <v/>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="25">
         <f>E25-H25</f>
         <v/>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="26">
         <f>IFERROR(H25/E25,0)</f>
         <v/>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L25" s="9">
+      <c r="L25" s="22">
         <f>IF(H25&gt;=E25,"Done",IF(H25&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2551,55 +2552,55 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
-        <is>
-          <t>INCIDENT</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Incident Data API Endpoints</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>MOD-BE</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>INCIDENTDESC</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Incident Descriptive Analytics</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>Jertz</t>
         </is>
       </c>
-      <c r="E26" s="28" t="n">
+      <c r="E26" s="23" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="F26" s="24" t="n">
         <v>2.832</v>
       </c>
-      <c r="F26" s="29" t="n">
-        <v>2.517</v>
-      </c>
-      <c r="G26" s="38" t="inlineStr">
+      <c r="G26" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H26" s="28">
+      <c r="H26" s="23">
         <f>IF(UPPER(G26)="Y",E26,IF(N26=0,F26,F26+(E26-F26)*M26/N26))</f>
         <v/>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="25">
         <f>E26-H26</f>
         <v/>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="26">
         <f>IFERROR(H26/E26,0)</f>
         <v/>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="22">
         <f>IF(H26&gt;=E26,"Done",IF(H26&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2613,55 +2614,55 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>INCIDENTDESC</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Incident Descriptive Analytics</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>EMISSDESC</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Emissions &amp; Sustainability Descriptive Analytics</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>MOD-ANA</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>Jertz</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="n">
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="n">
         <v>3.147</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="24" t="n">
         <v>2.832</v>
       </c>
-      <c r="G27" s="38" t="inlineStr">
+      <c r="G27" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H27" s="28">
+      <c r="H27" s="23">
         <f>IF(UPPER(G27)="Y",E27,IF(N27=0,F27,F27+(E27-F27)*M27/N27))</f>
         <v/>
       </c>
-      <c r="I27" s="30">
+      <c r="I27" s="25">
         <f>E27-H27</f>
         <v/>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="26">
         <f>IFERROR(H27/E27,0)</f>
         <v/>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L27" s="9">
+      <c r="L27" s="22">
         <f>IF(H27&gt;=E27,"Done",IF(H27&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2675,55 +2676,55 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>EMISSDESC</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Emissions &amp; Sustainability Descriptive Analytics</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>TRAFFICFC</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Traffic Volume Predictive Model</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>MOD-ANA</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>Hans</t>
         </is>
       </c>
-      <c r="E28" s="28" t="n">
-        <v>3.147</v>
-      </c>
-      <c r="F28" s="29" t="n">
+      <c r="E28" s="23" t="n">
+        <v>3.462</v>
+      </c>
+      <c r="F28" s="24" t="n">
         <v>2.832</v>
       </c>
-      <c r="G28" s="38" t="inlineStr">
+      <c r="G28" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H28" s="28">
+      <c r="H28" s="23">
         <f>IF(UPPER(G28)="Y",E28,IF(N28=0,F28,F28+(E28-F28)*M28/N28))</f>
         <v/>
       </c>
-      <c r="I28" s="30">
+      <c r="I28" s="25">
         <f>E28-H28</f>
         <v/>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="26">
         <f>IFERROR(H28/E28,0)</f>
         <v/>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L28" s="9">
+      <c r="L28" s="22">
         <f>IF(H28&gt;=E28,"Done",IF(H28&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2737,55 +2738,55 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>UPLOAD</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Data Upload &amp; Validation API</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>MOD-BE</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Ysa</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="n">
-        <v>2.203</v>
-      </c>
-      <c r="F29" s="29" t="n">
-        <v>1.888</v>
-      </c>
-      <c r="G29" s="38" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>INCIDENTFC</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>Incident Predictive Model</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="n">
+        <v>2.832</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H29" s="28">
+      <c r="H29" s="23">
         <f>IF(UPPER(G29)="Y",E29,IF(N29=0,F29,F29+(E29-F29)*M29/N29))</f>
         <v/>
       </c>
-      <c r="I29" s="30">
+      <c r="I29" s="25">
         <f>E29-H29</f>
         <v/>
       </c>
-      <c r="J29" s="31">
+      <c r="J29" s="26">
         <f>IFERROR(H29/E29,0)</f>
         <v/>
       </c>
-      <c r="K29" s="9" t="inlineStr">
-        <is>
-          <t>Oct 5 - Oct 6</t>
-        </is>
-      </c>
-      <c r="L29" s="9">
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>Sep 29 - Oct 3</t>
+        </is>
+      </c>
+      <c r="L29" s="22">
         <f>IF(H29&gt;=E29,"Done",IF(H29&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2799,55 +2800,55 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>DATAUP</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Data Management &amp; Upload Page</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>MOD-FE</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Kiarra</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="n">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>PRESCRIBE</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Prescriptive Optimization Models</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="n">
         <v>2.517</v>
       </c>
-      <c r="F30" s="29" t="n">
-        <v>2.517</v>
-      </c>
-      <c r="G30" s="38" t="inlineStr">
+      <c r="F30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H30" s="28">
+      <c r="H30" s="23">
         <f>IF(UPPER(G30)="Y",E30,IF(N30=0,F30,F30+(E30-F30)*M30/N30))</f>
         <v/>
       </c>
-      <c r="I30" s="30">
+      <c r="I30" s="25">
         <f>E30-H30</f>
         <v/>
       </c>
-      <c r="J30" s="31">
+      <c r="J30" s="26">
         <f>IFERROR(H30/E30,0)</f>
         <v/>
       </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>Oct 5 - Oct 6</t>
-        </is>
-      </c>
-      <c r="L30" s="9">
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>Sep 29 - Oct 3</t>
+        </is>
+      </c>
+      <c r="L30" s="22">
         <f>IF(H30&gt;=E30,"Done",IF(H30&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2861,55 +2862,55 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>REPO</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Repository &amp; Branch Management</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>CORE</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Kiarra</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="F31" s="29" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="G31" s="38" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>AGENT-M</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>Agent Simulation - vehicle dynamics &amp; calibration</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="n">
+        <v>1.101</v>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="G31" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H31" s="28">
+      <c r="H31" s="23">
         <f>IF(UPPER(G31)="Y",E31,IF(N31=0,F31,F31+(E31-F31)*M31/N31))</f>
         <v/>
       </c>
-      <c r="I31" s="30">
+      <c r="I31" s="25">
         <f>E31-H31</f>
         <v/>
       </c>
-      <c r="J31" s="31">
+      <c r="J31" s="26">
         <f>IFERROR(H31/E31,0)</f>
         <v/>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L31" s="9">
+      <c r="L31" s="22">
         <f>IF(H31&gt;=E31,"Done",IF(H31&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2923,55 +2924,55 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
-        <is>
-          <t>UIUX</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Global UI/UX Design System</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>MOD-FE</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>Kiarra</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="F32" s="29" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="G32" s="38" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>AGENT-S</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Agent Simulation - scenarios &amp; validation</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Jertz</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="G32" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H32" s="28">
+      <c r="H32" s="23">
         <f>IF(UPPER(G32)="Y",E32,IF(N32=0,F32,F32+(E32-F32)*M32/N32))</f>
         <v/>
       </c>
-      <c r="I32" s="30">
+      <c r="I32" s="25">
         <f>E32-H32</f>
         <v/>
       </c>
-      <c r="J32" s="31">
+      <c r="J32" s="26">
         <f>IFERROR(H32/E32,0)</f>
         <v/>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="22" t="inlineStr">
         <is>
           <t>Oct 5 - Oct 6</t>
         </is>
       </c>
-      <c r="L32" s="9">
+      <c r="L32" s="22">
         <f>IF(H32&gt;=E32,"Done",IF(H32&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -2985,55 +2986,55 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>ETL</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>ETL Pipeline &amp; Data Warehouse</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>MOD-DB</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>Hans</t>
-        </is>
-      </c>
-      <c r="E33" s="28" t="n">
-        <v>2.203</v>
-      </c>
-      <c r="F33" s="29" t="n">
-        <v>2.203</v>
-      </c>
-      <c r="G33" s="38" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>DESCOPED - delivered as an LLM layer instead. GLM via an OpenAI-compatible endpoint, with the ai-insight, ai-explain and sandbox-command services; ai-explain retrieves from the warehouse and grounds the prompt. Not built: document corpus, chunking, embeddings, vector index, Claude Sonnet, FastAPI. Confirm with the adviser that the substitution is accepted - 2.517 points ride on it.</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>Ysa</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="n">
+        <v>2.517</v>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H33" s="28">
+      <c r="H33" s="23">
         <f>IF(UPPER(G33)="Y",E33,IF(N33=0,F33,F33+(E33-F33)*M33/N33))</f>
         <v/>
       </c>
-      <c r="I33" s="30">
+      <c r="I33" s="25">
         <f>E33-H33</f>
         <v/>
       </c>
-      <c r="J33" s="31">
+      <c r="J33" s="26">
         <f>IFERROR(H33/E33,0)</f>
         <v/>
       </c>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>Oct 5 - Oct 6</t>
-        </is>
-      </c>
-      <c r="L33" s="9">
+      <c r="K33" s="22" t="inlineStr">
+        <is>
+          <t>Oct 3 - sign-off</t>
+        </is>
+      </c>
+      <c r="L33" s="22">
         <f>IF(H33&gt;=E33,"Done",IF(H33&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -3047,55 +3048,55 @@
       </c>
     </row>
     <row r="34" ht="46" customHeight="1">
-      <c r="A34" s="58" t="inlineStr">
-        <is>
-          <t>(unmapped)</t>
-        </is>
-      </c>
-      <c r="B34" s="59" t="inlineStr">
-        <is>
-          <t>Task IDs that repeat across modules in the acceptance-criteria PDF (AUTH, TRAFFIC, INCIDENT, SANDBOX, MAINT, MAPCOMP, SUSTAIN each appear twice at different weights). Split them out of the source file and replace this row with the real ones.</t>
-        </is>
-      </c>
-      <c r="C34" s="60" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="D34" s="60" t="inlineStr">
-        <is>
-          <t>unassigned</t>
-        </is>
-      </c>
-      <c r="E34" s="61" t="n">
-        <v>18.882</v>
-      </c>
-      <c r="F34" s="62" t="n">
-        <v>15.109</v>
-      </c>
-      <c r="G34" s="63" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>DATAPREP</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Analytics Data Preparation &amp; Integration</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>MOD-ANA</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="n">
+        <v>4.406</v>
+      </c>
+      <c r="F34" s="24" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="G34" s="57" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H34" s="61">
+      <c r="H34" s="23">
         <f>IF(UPPER(G34)="Y",E34,IF(N34=0,F34,F34+(E34-F34)*M34/N34))</f>
         <v/>
       </c>
-      <c r="I34" s="64">
+      <c r="I34" s="25">
         <f>E34-H34</f>
         <v/>
       </c>
-      <c r="J34" s="65">
+      <c r="J34" s="26">
         <f>IFERROR(H34/E34,0)</f>
         <v/>
       </c>
-      <c r="K34" s="60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="60">
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>Oct 4 - Oct 5</t>
+        </is>
+      </c>
+      <c r="L34" s="22">
         <f>IF(H34&gt;=E34,"Done",IF(H34&gt;0,"In progress","Not started"))</f>
         <v/>
       </c>
@@ -3109,43 +3110,521 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Core Traffic Data Schema &amp; Import Tables</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="inlineStr">
+        <is>
+          <t>MOD-DB</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="G35" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H35" s="23">
+        <f>IF(UPPER(G35)="Y",E35,IF(N35=0,F35,F35+(E35-F35)*M35/N35))</f>
+        <v/>
+      </c>
+      <c r="I35" s="25">
+        <f>E35-H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="26">
+        <f>IFERROR(H35/E35,0)</f>
+        <v/>
+      </c>
+      <c r="K35" s="22" t="inlineStr">
+        <is>
+          <t>Oct 4 - Oct 5</t>
+        </is>
+      </c>
+      <c r="L35" s="22">
+        <f>IF(H35&gt;=E35,"Done",IF(H35&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M35" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A35&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A35&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A35&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A35&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N35" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A35&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A35&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A35&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A35&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>ETL</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>ETL Pipeline &amp; Data Warehouse</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>MOD-DB</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="F36" s="24" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="G36" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H36" s="23">
+        <f>IF(UPPER(G36)="Y",E36,IF(N36=0,F36,F36+(E36-F36)*M36/N36))</f>
+        <v/>
+      </c>
+      <c r="I36" s="25">
+        <f>E36-H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="26">
+        <f>IFERROR(H36/E36,0)</f>
+        <v/>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L36" s="22">
+        <f>IF(H36&gt;=E36,"Done",IF(H36&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M36" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A36&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A36&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A36&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A36&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N36" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A36&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A36&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A36&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A36&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>CACHE</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Redis Cache &amp; Event Messaging Setup</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="inlineStr">
+        <is>
+          <t>MOD-DB</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="E37" s="23" t="n">
+        <v>1.888</v>
+      </c>
+      <c r="F37" s="24" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G37" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H37" s="23">
+        <f>IF(UPPER(G37)="Y",E37,IF(N37=0,F37,F37+(E37-F37)*M37/N37))</f>
+        <v/>
+      </c>
+      <c r="I37" s="25">
+        <f>E37-H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="26">
+        <f>IFERROR(H37/E37,0)</f>
+        <v/>
+      </c>
+      <c r="K37" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L37" s="22">
+        <f>IF(H37&gt;=E37,"Done",IF(H37&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M37" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A37&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A37&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A37&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A37&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N37" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A37&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A37&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A37&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A37&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>HOST</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Hosting &amp; Deployment Setup</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="F38" s="24" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="G38" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H38" s="23">
+        <f>IF(UPPER(G38)="Y",E38,IF(N38=0,F38,F38+(E38-F38)*M38/N38))</f>
+        <v/>
+      </c>
+      <c r="I38" s="25">
+        <f>E38-H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="26">
+        <f>IFERROR(H38/E38,0)</f>
+        <v/>
+      </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L38" s="22">
+        <f>IF(H38&gt;=E38,"Done",IF(H38&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M38" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A38&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A38&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A38&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A38&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N38" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A38&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A38&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A38&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A38&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>REPO</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Repository &amp; Branch Management</t>
+        </is>
+      </c>
+      <c r="C39" s="22" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E39" s="23" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="F39" s="24" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G39" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H39" s="23">
+        <f>IF(UPPER(G39)="Y",E39,IF(N39=0,F39,F39+(E39-F39)*M39/N39))</f>
+        <v/>
+      </c>
+      <c r="I39" s="25">
+        <f>E39-H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="26">
+        <f>IFERROR(H39/E39,0)</f>
+        <v/>
+      </c>
+      <c r="K39" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L39" s="22">
+        <f>IF(H39&gt;=E39,"Done",IF(H39&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M39" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A39&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A39&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A39&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A39&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N39" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A39&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A39&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A39&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A39&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>ENV</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Environment Configuration</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="n">
+        <v>1.259</v>
+      </c>
+      <c r="F40" s="24" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="G40" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H40" s="23">
+        <f>IF(UPPER(G40)="Y",E40,IF(N40=0,F40,F40+(E40-F40)*M40/N40))</f>
+        <v/>
+      </c>
+      <c r="I40" s="25">
+        <f>E40-H40</f>
+        <v/>
+      </c>
+      <c r="J40" s="26">
+        <f>IFERROR(H40/E40,0)</f>
+        <v/>
+      </c>
+      <c r="K40" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L40" s="22">
+        <f>IF(H40&gt;=E40,"Done",IF(H40&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M40" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A40&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A40&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A40&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A40&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N40" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A40&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A40&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A40&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A40&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>UIUX</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Global UI/UX Design System</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="F41" s="24" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G41" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H41" s="23">
+        <f>IF(UPPER(G41)="Y",E41,IF(N41=0,F41,F41+(E41-F41)*M41/N41))</f>
+        <v/>
+      </c>
+      <c r="I41" s="25">
+        <f>E41-H41</f>
+        <v/>
+      </c>
+      <c r="J41" s="26">
+        <f>IFERROR(H41/E41,0)</f>
+        <v/>
+      </c>
+      <c r="K41" s="22" t="inlineStr">
+        <is>
+          <t>Oct 5 - Oct 6</t>
+        </is>
+      </c>
+      <c r="L41" s="22">
+        <f>IF(H41&gt;=E41,"Done",IF(H41&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M41" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A41&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A41&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A41&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A41&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N41" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A41&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A41&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A41&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A41&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Pm</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>CORE</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>Kiarra</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="F42" s="24" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G42" s="57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H42" s="23">
+        <f>IF(UPPER(G42)="Y",E42,IF(N42=0,F42,F42+(E42-F42)*M42/N42))</f>
+        <v/>
+      </c>
+      <c r="I42" s="25">
+        <f>E42-H42</f>
+        <v/>
+      </c>
+      <c r="J42" s="26">
+        <f>IFERROR(H42/E42,0)</f>
+        <v/>
+      </c>
+      <c r="K42" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="22">
+        <f>IF(H42&gt;=E42,"Done",IF(H42&gt;0,"In progress","Not started"))</f>
+        <v/>
+      </c>
+      <c r="M42" s="69">
+        <f>COUNTIFS(Kiarra!$I:$I,"*;"&amp;$A42&amp;";*",Kiarra!$H:$H,"Done")+COUNTIFS(Hans!$I:$I,"*;"&amp;$A42&amp;";*",Hans!$H:$H,"Done")+COUNTIFS(Jertz!$I:$I,"*;"&amp;$A42&amp;";*",Jertz!$H:$H,"Done")+COUNTIFS(Ysa!$I:$I,"*;"&amp;$A42&amp;";*",Ysa!$H:$H,"Done")</f>
+        <v/>
+      </c>
+      <c r="N42" s="69">
+        <f>COUNTIF(Kiarra!$I:$I,"*;"&amp;$A42&amp;";*")+COUNTIF(Hans!$I:$I,"*;"&amp;$A42&amp;";*")+COUNTIF(Jertz!$I:$I,"*;"&amp;$A42&amp;";*")+COUNTIF(Ysa!$I:$I,"*;"&amp;$A42&amp;";*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="17">
-        <f>SUM(E5:E34)</f>
-        <v/>
-      </c>
-      <c r="F35" s="17">
-        <f>SUM(F5:F34)</f>
-        <v/>
-      </c>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="17">
-        <f>SUM(H5:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="17">
-        <f>SUM(I5:I34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="11">
-        <f>IFERROR(H35/E35,0)</f>
-        <v/>
-      </c>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="10">
-        <f>SUM(M5:M34)</f>
-        <v/>
-      </c>
-      <c r="N35" s="10">
-        <f>SUM(N5:N34)</f>
+      <c r="E43" s="82">
+        <f>SUM(E5:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="82">
+        <f>SUM(F5:F42)</f>
+        <v/>
+      </c>
+      <c r="H43" s="82">
+        <f>SUM(H5:H42)</f>
+        <v/>
+      </c>
+      <c r="I43" s="82">
+        <f>SUM(I5:I42)</f>
         <v/>
       </c>
     </row>
@@ -3882,22 +4361,22 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>The Priority Board carries a 3.773-point (unmapped) row - task IDs that repeat across modules in the acceptance PDF (AUTH, TRAFFIC, INCIDENT, SANDBOX, MAINT, MAPCOMP, SUSTAIN each appear twice at different weights). Open the source file, split them by module, and replace that row with the real ones.</t>
+          <t>Split the acceptance file's repeated task IDs by module. DONE 7 Oct. The row was 18.882 points, not the 3.773 this block assumed - 21% of the entire system weight, owned by nobody. Seven IDs repeat across MOD-FE and MOD-BE at different weights (AUTH is 1.888 on the frontend and 2.517 on the backend, and so on). The PDF does not label which table belongs to which module, so each column was summed and matched against the module totals printed on the same page; all five match to within decimal rounding, so the assignment is evidence, not a guess. The board now carries 38 task rows across MOD-FE/BE/ANA/DB/CORE and no (unmapped) row. NOTE: it totals 89.999, not 90.000. The source states every weight to three decimals and 38 of them do not re-sum exactly; the PDF's own module subtotals add to 90.001. The thousandth was left rather than fudged into a row to make the figure look round.</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>The (unmapped) row is gone and the board still totals 90.000.</t>
+          <t>The (unmapped) row is gone and every task sits under its real module.</t>
         </is>
       </c>
       <c r="H18" s="38" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I18" s="70" t="inlineStr">
         <is>
-          <t>;(unmapped);</t>
+          <t>(overhead)</t>
         </is>
       </c>
       <c r="J18" s="78" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -4317,7 +4317,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Migrate ESLint to flat config (eslint.config.js). ESLint 9 cannot read the legacy .eslintrc, so `npx eslint` has never run standalone - note that `next build` does run it, so this is about making the standalone lint step real, which 3.13 SQA claims exists.</t>
+          <t>Migrate ESLint to flat config. DONE 7 Oct. Confirmed broken first: npx eslint . exited 2 with "couldn't find an eslint.config file" - ESLint 9 was declared but configured through .eslintrc.json, which v9 no longer reads. next build lints anyway because Next shims the old format internally, which is why nobody noticed the standalone step had never worked, while 3.13 SQA describes it as part of the process. Added eslint.config.mjs using FlatCompat (eslint-config-next ships no flat entry yet), so the rule set is unchanged - only how it loads. Result: npx eslint . exits 0, 0 errors, 83 warnings. The 3 errors it first reported were require() in electron/main.js and preload.js; Electron loads both as CommonJS by requirement, so the rule is off for electron/** rather than the calls being worked around. FOLLOW-UP: .eslintrc.json is still on disk. It is dead to ESLint 9 but next build may still read it; delete it and re-run a full build to confirm, which needs the dev server stopped.</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="H17" s="38" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I17" s="71" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -4515,7 +4515,7 @@
       </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
-          <t>Contrast and accessibility sweep across every page in both themes. Fix what fails.</t>
+          <t>Contrast and accessibility sweep across every page in both themes. DONE 7 Oct, nothing to fix. 10 dashboard pages x light and dark = 20 runs, ~10,000 text-bearing elements scored against the surface each is actually painted on, walking up the tree for transparent backgrounds. Result: 0 elements below 3:1. Theme switching was verified separately rather than assumed - light resolves --bg-body to #eef5fd and dark to #0a1838, with data-theme set on the root - because light and dark returned identical element counts and that would also be the signature of the theme never switching. CAVEAT: 4-6 elements per page sit on a gradient or image and are reported, not scored; a single computed background cannot represent what is behind them. Those need an eye, not a probe. The NLEX Daylight redesign held contrast well - this found nothing to fix.</t>
         </is>
       </c>
       <c r="G22" s="41" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H22" s="42" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I22" s="71" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>Close the remaining Data Management and Upload Page subtasks.</t>
+          <t>Close the remaining Data Management and Upload Page subtasks. DONE 7 Oct - there were none remaining. The acceptance file already records all 8 DATAUP subtasks complete (2.517 of 2.517), including its UAT-01. What was worth checking is that the page still works after the upload endpoints went behind authenticateToken + data-analyst on 1 Oct: /history, /formats and /retraining all answer 401 without a token and 200 with one, and the page routes every call through lib/api.ts, so it carries the session. No regression. NOTE: UPLOAD (2.203/1.888, the backend half of the same page) is Ysa's, not this block's.</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="H24" s="38" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I24" s="70" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -4471,7 +4471,7 @@
       </c>
       <c r="F21" s="41" t="inlineStr">
         <is>
-          <t>Work the bracketed values through Chapter 4 - every [insert number] and [insert percentage]. Note 1 in the draft warns the sentence around each may need rewording where the real data contradicts the placeholder phrasing, so read each one rather than find-and-replacing.</t>
+          <t>Work the bracketed values through Chapter 4. DONE 8 Oct -&gt; Chapter4_Revised_4.1_Results.md. Every placeholder in 4.1 replaced with a value read from the warehouse or the endpoint that renders the matching panel; 15 computed figures re-checked by arithmetic. Note 1 was right: 5 claims run the WRONG WAY. Holidays are 20 of 21 BELOW baseline (Good Friday -49%), not above. Wet weather raises CRASHES 19.3% but not incidents overall (breakdowns outnumber crashes 8:1 and are slightly lower in wet). Observed jam speed is HIGHER in wet, not lower. Volume champion is Prophet, not LSTM (rank 7 of 8, rejected). At the 90/10 split NOTHING is accepted. Also: incident champion carries an OVERFITTING diagnosis; 9 named analyses are not implemented in the build; the emission strategy panel is hardcoded ILLUSTRATIVE; and non-Waze speed is SYNTHETIC per the warehouse's own evaluation records - that disclosure is not in the draft at all. 16 corrections listed in section 4.1.6.</t>
         </is>
       </c>
       <c r="G21" s="41" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="H21" s="42" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I21" s="70" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -4559,7 +4559,7 @@
       </c>
       <c r="F23" s="41" t="inlineStr">
         <is>
-          <t>Replace the mock-ups in 3.7 (p165) with screenshots of what shipped. The predictive tabs, scenario sandbox and map panels were all redesigned during development.</t>
+          <t>Replace the mock-ups in 3.7 with screenshots of what shipped. DONE 8 Oct, via Chapter 4: 32 panels captured live from the running dashboard and embedded, plus the 4 existing figures = 36. MFA blocked this at first - the shell now drops a password-only (aal1) session, so a scripted login appeared to work then silently signed itself out. Enrolled TOTP on a fresh capture account to mint an aal2 session. TWO PANELS IN THE DRAFT NO LONGER EXIST: Secondary Incident Risk and Time to Clear are gone, replaced by Response Time Breakdown and Predicted Median Response Time - those screenshots must be swapped. THREE PANELS PREVIOUSLY CALLED MISSING NOW EXIST: Booth Staffing Plan, Congestion Response Advisory, and the emission strategies, which are now COMPUTED (3.39/0.48/0.33%), not the old hardcoded Strategy A/B/C mock.</t>
         </is>
       </c>
       <c r="G23" s="41" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="H23" s="42" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="I23" s="70" t="inlineStr">

--- a/SmartFlow_Sprint_Planner.xlsx
+++ b/SmartFlow_Sprint_Planner.xlsx
@@ -1144,7 +1144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>Incident Predictive Model</t>
+          <t>Incident Predictive Model — re-scored 15 Oct: NegBinomial_GLM champion, 7 models benchmarked, 90-day forecast live; EVAL-01 and DEP-01 evidenced. UAT-01 and MS-01 outstanding.</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -2762,7 +2762,7 @@
         <v>2.832</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>0</v>
+        <v>2.264</v>
       </c>
       <c r="G29" s="57" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>Prescriptive Optimization Models</t>
+          <t>Prescriptive Optimization Models — re-scored 15 Oct: Booth Staffing, Congestion Response Advisory, Resource Staging, Patrol Alert Schedule and computed emission strategies all live; Monte Carlo (MODEL-04) implemented at 400 seeded runs. EVAL-01 and MS-01 outstanding.</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -2824,7 +2824,7 @@
         <v>2.517</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>0</v>
+        <v>2.014</v>
       </c>
       <c r="G30" s="57" t="inlineStr">
         <is>
@@ -3628,6 +3628,12 @@
         <v/>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <autoFilter ref="A4:L34"/>
   <mergeCells count="1">
